--- a/ams/cases/npcc/npcc_uced.xlsx
+++ b/ams/cases/npcc/npcc_uced.xlsx
@@ -15,9 +15,9 @@
     <sheet name="Line" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Zone" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="GCost" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="EDTSlot" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="EDSlot" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="EDSlotGen" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="UCTSlot" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="UCSlot" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="SFR" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="SFRCost" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="SR" sheetId="14" state="visible" r:id="rId14"/>

--- a/ams/cases/npcc/npcc_uced.xlsx
+++ b/ams/cases/npcc/npcc_uced.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Load factor in EDTSlot and UCTSlot sourced from ISO-NE day-ahead cleared hourly load on 2022 June 29</t>
+          <t>Load factor in EDSlotLoad and UCSlotLoad sourced from ISO-NE day-ahead cleared hourly load on 2022 June 29</t>
         </is>
       </c>
     </row>
